--- a/artfynd/A 29387-2025 artfynd.xlsx
+++ b/artfynd/A 29387-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126826562</v>
       </c>
       <c r="B2" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>126826277</v>
       </c>
       <c r="B3" t="n">
-        <v>105396</v>
+        <v>105471</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>126760235</v>
       </c>
       <c r="B4" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>126826308</v>
       </c>
       <c r="B5" t="n">
-        <v>105396</v>
+        <v>105471</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>126848655</v>
       </c>
       <c r="B6" t="n">
-        <v>91265</v>
+        <v>91339</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         <v>126848714</v>
       </c>
       <c r="B7" t="n">
-        <v>91210</v>
+        <v>91284</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>126848794</v>
       </c>
       <c r="B8" t="n">
-        <v>91866</v>
+        <v>91940</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>126848641</v>
       </c>
       <c r="B9" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 29387-2025 artfynd.xlsx
+++ b/artfynd/A 29387-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126826562</v>
       </c>
       <c r="B2" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>126826277</v>
       </c>
       <c r="B3" t="n">
-        <v>105471</v>
+        <v>105477</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>126760235</v>
       </c>
       <c r="B4" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>126826308</v>
       </c>
       <c r="B5" t="n">
-        <v>105471</v>
+        <v>105477</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>126848655</v>
       </c>
       <c r="B6" t="n">
-        <v>91339</v>
+        <v>91345</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         <v>126848714</v>
       </c>
       <c r="B7" t="n">
-        <v>91284</v>
+        <v>91290</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>126848794</v>
       </c>
       <c r="B8" t="n">
-        <v>91940</v>
+        <v>91946</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>126848641</v>
       </c>
       <c r="B9" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 29387-2025 artfynd.xlsx
+++ b/artfynd/A 29387-2025 artfynd.xlsx
@@ -779,7 +779,7 @@
         <v>126826277</v>
       </c>
       <c r="B3" t="n">
-        <v>105477</v>
+        <v>105478</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>126826308</v>
       </c>
       <c r="B5" t="n">
-        <v>105477</v>
+        <v>105478</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>126848655</v>
       </c>
       <c r="B6" t="n">
-        <v>91345</v>
+        <v>91346</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         <v>126848714</v>
       </c>
       <c r="B7" t="n">
-        <v>91290</v>
+        <v>91291</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>126848794</v>
       </c>
       <c r="B8" t="n">
-        <v>91946</v>
+        <v>91947</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 29387-2025 artfynd.xlsx
+++ b/artfynd/A 29387-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126826562</v>
       </c>
       <c r="B2" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>126826277</v>
       </c>
       <c r="B3" t="n">
-        <v>105478</v>
+        <v>105484</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>126760235</v>
       </c>
       <c r="B4" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>126826308</v>
       </c>
       <c r="B5" t="n">
-        <v>105478</v>
+        <v>105484</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>126848655</v>
       </c>
       <c r="B6" t="n">
-        <v>91346</v>
+        <v>91350</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         <v>126848714</v>
       </c>
       <c r="B7" t="n">
-        <v>91291</v>
+        <v>91295</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1293,10 +1293,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126848794</v>
+        <v>126848641</v>
       </c>
       <c r="B8" t="n">
-        <v>91947</v>
+        <v>79636</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1304,21 +1304,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5454</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1331,10 +1331,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>560633</v>
+        <v>560608</v>
       </c>
       <c r="R8" t="n">
-        <v>6462133</v>
+        <v>6462081</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126848641</v>
+        <v>126848794</v>
       </c>
       <c r="B9" t="n">
-        <v>79632</v>
+        <v>91951</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>5454</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1432,10 +1432,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>560608</v>
+        <v>560633</v>
       </c>
       <c r="R9" t="n">
-        <v>6462081</v>
+        <v>6462133</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1498,7 +1498,7 @@
         <v>126848471</v>
       </c>
       <c r="B10" t="n">
-        <v>5492</v>
+        <v>5493</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 29387-2025 artfynd.xlsx
+++ b/artfynd/A 29387-2025 artfynd.xlsx
@@ -1293,10 +1293,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126848641</v>
+        <v>126848794</v>
       </c>
       <c r="B8" t="n">
-        <v>79636</v>
+        <v>91951</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1304,21 +1304,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>5454</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1331,10 +1331,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>560608</v>
+        <v>560633</v>
       </c>
       <c r="R8" t="n">
-        <v>6462081</v>
+        <v>6462133</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126848794</v>
+        <v>126848641</v>
       </c>
       <c r="B9" t="n">
-        <v>91951</v>
+        <v>79636</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5454</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1432,10 +1432,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>560633</v>
+        <v>560608</v>
       </c>
       <c r="R9" t="n">
-        <v>6462133</v>
+        <v>6462081</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>

--- a/artfynd/A 29387-2025 artfynd.xlsx
+++ b/artfynd/A 29387-2025 artfynd.xlsx
@@ -779,7 +779,7 @@
         <v>126826277</v>
       </c>
       <c r="B3" t="n">
-        <v>105484</v>
+        <v>105486</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>126826308</v>
       </c>
       <c r="B5" t="n">
-        <v>105484</v>
+        <v>105486</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 29387-2025 artfynd.xlsx
+++ b/artfynd/A 29387-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1596,6 +1596,231 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>127748895</v>
+      </c>
+      <c r="B11" t="n">
+        <v>96052</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hattberget/Risten, Ög</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>560796</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6462042</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Flera</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Charlotte Erbs</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Charlotte Erbs</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>127748920</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57823</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hattberget/Risten, Ög</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>560789</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6462042</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Hört från två håll</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Charlotte Erbs</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Charlotte Erbs</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29387-2025 artfynd.xlsx
+++ b/artfynd/A 29387-2025 artfynd.xlsx
@@ -1601,7 +1601,7 @@
         <v>127748895</v>
       </c>
       <c r="B11" t="n">
-        <v>96052</v>
+        <v>96058</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 29387-2025 artfynd.xlsx
+++ b/artfynd/A 29387-2025 artfynd.xlsx
@@ -1601,7 +1601,7 @@
         <v>127748895</v>
       </c>
       <c r="B11" t="n">
-        <v>96058</v>
+        <v>96061</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>127748920</v>
       </c>
       <c r="B12" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 29387-2025 artfynd.xlsx
+++ b/artfynd/A 29387-2025 artfynd.xlsx
@@ -1601,7 +1601,7 @@
         <v>127748895</v>
       </c>
       <c r="B11" t="n">
-        <v>96061</v>
+        <v>96069</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>127748920</v>
       </c>
       <c r="B12" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 29387-2025 artfynd.xlsx
+++ b/artfynd/A 29387-2025 artfynd.xlsx
@@ -1601,7 +1601,7 @@
         <v>127748895</v>
       </c>
       <c r="B11" t="n">
-        <v>96069</v>
+        <v>96070</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 29387-2025 artfynd.xlsx
+++ b/artfynd/A 29387-2025 artfynd.xlsx
@@ -1601,7 +1601,7 @@
         <v>127748895</v>
       </c>
       <c r="B11" t="n">
-        <v>96070</v>
+        <v>96071</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 29387-2025 artfynd.xlsx
+++ b/artfynd/A 29387-2025 artfynd.xlsx
@@ -1601,7 +1601,7 @@
         <v>127748895</v>
       </c>
       <c r="B11" t="n">
-        <v>96071</v>
+        <v>96072</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 29387-2025 artfynd.xlsx
+++ b/artfynd/A 29387-2025 artfynd.xlsx
@@ -1601,7 +1601,7 @@
         <v>127748895</v>
       </c>
       <c r="B11" t="n">
-        <v>96072</v>
+        <v>96080</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>127748920</v>
       </c>
       <c r="B12" t="n">
-        <v>57832</v>
+        <v>57833</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 29387-2025 artfynd.xlsx
+++ b/artfynd/A 29387-2025 artfynd.xlsx
@@ -1601,7 +1601,7 @@
         <v>127748895</v>
       </c>
       <c r="B11" t="n">
-        <v>96080</v>
+        <v>96173</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>127748920</v>
       </c>
       <c r="B12" t="n">
-        <v>57833</v>
+        <v>57845</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 29387-2025 artfynd.xlsx
+++ b/artfynd/A 29387-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126826562</v>
       </c>
       <c r="B2" t="n">
-        <v>79636</v>
+        <v>79629</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>126826277</v>
       </c>
       <c r="B3" t="n">
-        <v>105486</v>
+        <v>105471</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>126760235</v>
       </c>
       <c r="B4" t="n">
-        <v>79636</v>
+        <v>79629</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>126826308</v>
       </c>
       <c r="B5" t="n">
-        <v>105486</v>
+        <v>105471</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>126848655</v>
       </c>
       <c r="B6" t="n">
-        <v>91350</v>
+        <v>91339</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         <v>126848714</v>
       </c>
       <c r="B7" t="n">
-        <v>91295</v>
+        <v>91284</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>126848794</v>
       </c>
       <c r="B8" t="n">
-        <v>91951</v>
+        <v>91940</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>126848641</v>
       </c>
       <c r="B9" t="n">
-        <v>79636</v>
+        <v>79629</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>126848471</v>
       </c>
       <c r="B10" t="n">
-        <v>5493</v>
+        <v>5492</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 29387-2025 artfynd.xlsx
+++ b/artfynd/A 29387-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126826562</v>
       </c>
       <c r="B2" t="n">
-        <v>79629</v>
+        <v>79636</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>126826277</v>
       </c>
       <c r="B3" t="n">
-        <v>105471</v>
+        <v>105486</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>126760235</v>
       </c>
       <c r="B4" t="n">
-        <v>79629</v>
+        <v>79636</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>126826308</v>
       </c>
       <c r="B5" t="n">
-        <v>105471</v>
+        <v>105486</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>126848655</v>
       </c>
       <c r="B6" t="n">
-        <v>91339</v>
+        <v>91350</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         <v>126848714</v>
       </c>
       <c r="B7" t="n">
-        <v>91284</v>
+        <v>91295</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>126848794</v>
       </c>
       <c r="B8" t="n">
-        <v>91940</v>
+        <v>91951</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>126848641</v>
       </c>
       <c r="B9" t="n">
-        <v>79629</v>
+        <v>79636</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>126848471</v>
       </c>
       <c r="B10" t="n">
-        <v>5492</v>
+        <v>5493</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 29387-2025 artfynd.xlsx
+++ b/artfynd/A 29387-2025 artfynd.xlsx
@@ -1933,7 +1933,7 @@
         <v>130466908</v>
       </c>
       <c r="B14" t="n">
-        <v>105987</v>
+        <v>105990</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>130466980</v>
       </c>
       <c r="B15" t="n">
-        <v>97166</v>
+        <v>97169</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>130466830</v>
       </c>
       <c r="B17" t="n">
-        <v>79799</v>
+        <v>79802</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2342,49 +2342,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130466886</v>
+        <v>130467034</v>
       </c>
       <c r="B18" t="n">
-        <v>105987</v>
+        <v>91752</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221144</v>
+        <v>5442</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ö Hattberget, Ög</t>
+          <t>Hattberget, Ög</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>560839</v>
+        <v>560569</v>
       </c>
       <c r="R18" t="n">
-        <v>6462220</v>
+        <v>6462203</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2444,48 +2443,49 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130467034</v>
+        <v>130466886</v>
       </c>
       <c r="B19" t="n">
-        <v>91749</v>
+        <v>105990</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5442</v>
+        <v>221144</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hattberget, Ög</t>
+          <t>Ö Hattberget, Ög</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>560569</v>
+        <v>560839</v>
       </c>
       <c r="R19" t="n">
-        <v>6462203</v>
+        <v>6462220</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2548,7 +2548,7 @@
         <v>130467204</v>
       </c>
       <c r="B20" t="n">
-        <v>78846</v>
+        <v>78849</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>130467073</v>
       </c>
       <c r="B21" t="n">
-        <v>91749</v>
+        <v>91752</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         <v>130467122</v>
       </c>
       <c r="B22" t="n">
-        <v>91785</v>
+        <v>91788</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>130466789</v>
       </c>
       <c r="B23" t="n">
-        <v>97798</v>
+        <v>97801</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 29387-2025 artfynd.xlsx
+++ b/artfynd/A 29387-2025 artfynd.xlsx
@@ -1933,7 +1933,7 @@
         <v>130466908</v>
       </c>
       <c r="B14" t="n">
-        <v>105990</v>
+        <v>106016</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>130466980</v>
       </c>
       <c r="B15" t="n">
-        <v>97169</v>
+        <v>97195</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>130466830</v>
       </c>
       <c r="B17" t="n">
-        <v>79802</v>
+        <v>79828</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>130467034</v>
       </c>
       <c r="B18" t="n">
-        <v>91752</v>
+        <v>91778</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>130466886</v>
       </c>
       <c r="B19" t="n">
-        <v>105990</v>
+        <v>106016</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         <v>130467204</v>
       </c>
       <c r="B20" t="n">
-        <v>78849</v>
+        <v>78875</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>130467073</v>
       </c>
       <c r="B21" t="n">
-        <v>91752</v>
+        <v>91778</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         <v>130467122</v>
       </c>
       <c r="B22" t="n">
-        <v>91788</v>
+        <v>91814</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>130466789</v>
       </c>
       <c r="B23" t="n">
-        <v>97801</v>
+        <v>97827</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 29387-2025 artfynd.xlsx
+++ b/artfynd/A 29387-2025 artfynd.xlsx
@@ -1933,7 +1933,7 @@
         <v>130466908</v>
       </c>
       <c r="B14" t="n">
-        <v>106016</v>
+        <v>106017</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>130466980</v>
       </c>
       <c r="B15" t="n">
-        <v>97195</v>
+        <v>97196</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>130467034</v>
       </c>
       <c r="B18" t="n">
-        <v>91778</v>
+        <v>91779</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>130466886</v>
       </c>
       <c r="B19" t="n">
-        <v>106016</v>
+        <v>106017</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>130467073</v>
       </c>
       <c r="B21" t="n">
-        <v>91778</v>
+        <v>91779</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         <v>130467122</v>
       </c>
       <c r="B22" t="n">
-        <v>91814</v>
+        <v>91815</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>130466789</v>
       </c>
       <c r="B23" t="n">
-        <v>97827</v>
+        <v>97828</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 29387-2025 artfynd.xlsx
+++ b/artfynd/A 29387-2025 artfynd.xlsx
@@ -1933,7 +1933,7 @@
         <v>130466908</v>
       </c>
       <c r="B14" t="n">
-        <v>106017</v>
+        <v>106018</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>130466980</v>
       </c>
       <c r="B15" t="n">
-        <v>97196</v>
+        <v>97197</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>130467034</v>
       </c>
       <c r="B18" t="n">
-        <v>91779</v>
+        <v>91780</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>130466886</v>
       </c>
       <c r="B19" t="n">
-        <v>106017</v>
+        <v>106018</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>130467073</v>
       </c>
       <c r="B21" t="n">
-        <v>91779</v>
+        <v>91780</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         <v>130467122</v>
       </c>
       <c r="B22" t="n">
-        <v>91815</v>
+        <v>91816</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>130466789</v>
       </c>
       <c r="B23" t="n">
-        <v>97828</v>
+        <v>97829</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 29387-2025 artfynd.xlsx
+++ b/artfynd/A 29387-2025 artfynd.xlsx
@@ -1933,7 +1933,7 @@
         <v>130466908</v>
       </c>
       <c r="B14" t="n">
-        <v>106018</v>
+        <v>106020</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>130466980</v>
       </c>
       <c r="B15" t="n">
-        <v>97197</v>
+        <v>97199</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>130466830</v>
       </c>
       <c r="B17" t="n">
-        <v>79828</v>
+        <v>79830</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2342,48 +2342,49 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130467034</v>
+        <v>130466886</v>
       </c>
       <c r="B18" t="n">
-        <v>91780</v>
+        <v>106020</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5442</v>
+        <v>221144</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hattberget, Ög</t>
+          <t>Ö Hattberget, Ög</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>560569</v>
+        <v>560839</v>
       </c>
       <c r="R18" t="n">
-        <v>6462203</v>
+        <v>6462220</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2443,49 +2444,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130466886</v>
+        <v>130467034</v>
       </c>
       <c r="B19" t="n">
-        <v>106018</v>
+        <v>91782</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221144</v>
+        <v>5442</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ö Hattberget, Ög</t>
+          <t>Hattberget, Ög</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>560839</v>
+        <v>560569</v>
       </c>
       <c r="R19" t="n">
-        <v>6462220</v>
+        <v>6462203</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2548,7 +2548,7 @@
         <v>130467204</v>
       </c>
       <c r="B20" t="n">
-        <v>78875</v>
+        <v>78877</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>130467073</v>
       </c>
       <c r="B21" t="n">
-        <v>91780</v>
+        <v>91782</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         <v>130467122</v>
       </c>
       <c r="B22" t="n">
-        <v>91816</v>
+        <v>91818</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>130466789</v>
       </c>
       <c r="B23" t="n">
-        <v>97829</v>
+        <v>97831</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 29387-2025 artfynd.xlsx
+++ b/artfynd/A 29387-2025 artfynd.xlsx
@@ -1933,7 +1933,7 @@
         <v>130466908</v>
       </c>
       <c r="B14" t="n">
-        <v>106020</v>
+        <v>106024</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>130466980</v>
       </c>
       <c r="B15" t="n">
-        <v>97199</v>
+        <v>97203</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2342,49 +2342,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130466886</v>
+        <v>130467034</v>
       </c>
       <c r="B18" t="n">
-        <v>106020</v>
+        <v>91782</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221144</v>
+        <v>5442</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ö Hattberget, Ög</t>
+          <t>Hattberget, Ög</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>560839</v>
+        <v>560569</v>
       </c>
       <c r="R18" t="n">
-        <v>6462220</v>
+        <v>6462203</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2444,48 +2443,49 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130467034</v>
+        <v>130466886</v>
       </c>
       <c r="B19" t="n">
-        <v>91782</v>
+        <v>106024</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5442</v>
+        <v>221144</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hattberget, Ög</t>
+          <t>Ö Hattberget, Ög</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>560569</v>
+        <v>560839</v>
       </c>
       <c r="R19" t="n">
-        <v>6462203</v>
+        <v>6462220</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2851,7 +2851,7 @@
         <v>130466789</v>
       </c>
       <c r="B23" t="n">
-        <v>97831</v>
+        <v>97835</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 29387-2025 artfynd.xlsx
+++ b/artfynd/A 29387-2025 artfynd.xlsx
@@ -2342,48 +2342,49 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130467034</v>
+        <v>130466886</v>
       </c>
       <c r="B18" t="n">
-        <v>91782</v>
+        <v>106024</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5442</v>
+        <v>221144</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hattberget, Ög</t>
+          <t>Ö Hattberget, Ög</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>560569</v>
+        <v>560839</v>
       </c>
       <c r="R18" t="n">
-        <v>6462203</v>
+        <v>6462220</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2443,49 +2444,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130466886</v>
+        <v>130467034</v>
       </c>
       <c r="B19" t="n">
-        <v>106024</v>
+        <v>91782</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221144</v>
+        <v>5442</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ö Hattberget, Ög</t>
+          <t>Hattberget, Ög</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>560839</v>
+        <v>560569</v>
       </c>
       <c r="R19" t="n">
-        <v>6462220</v>
+        <v>6462203</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 29387-2025 artfynd.xlsx
+++ b/artfynd/A 29387-2025 artfynd.xlsx
@@ -2342,49 +2342,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130466886</v>
+        <v>130467034</v>
       </c>
       <c r="B18" t="n">
-        <v>106024</v>
+        <v>91782</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221144</v>
+        <v>5442</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ö Hattberget, Ög</t>
+          <t>Hattberget, Ög</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>560839</v>
+        <v>560569</v>
       </c>
       <c r="R18" t="n">
-        <v>6462220</v>
+        <v>6462203</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2444,48 +2443,49 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130467034</v>
+        <v>130466886</v>
       </c>
       <c r="B19" t="n">
-        <v>91782</v>
+        <v>106024</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5442</v>
+        <v>221144</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hattberget, Ög</t>
+          <t>Ö Hattberget, Ög</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>560569</v>
+        <v>560839</v>
       </c>
       <c r="R19" t="n">
-        <v>6462203</v>
+        <v>6462220</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 29387-2025 artfynd.xlsx
+++ b/artfynd/A 29387-2025 artfynd.xlsx
@@ -1933,7 +1933,7 @@
         <v>130466908</v>
       </c>
       <c r="B14" t="n">
-        <v>106024</v>
+        <v>106037</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>130466980</v>
       </c>
       <c r="B15" t="n">
-        <v>97203</v>
+        <v>97216</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>130466830</v>
       </c>
       <c r="B17" t="n">
-        <v>79830</v>
+        <v>79838</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>130467034</v>
       </c>
       <c r="B18" t="n">
-        <v>91782</v>
+        <v>91795</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>130466886</v>
       </c>
       <c r="B19" t="n">
-        <v>106024</v>
+        <v>106037</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         <v>130467204</v>
       </c>
       <c r="B20" t="n">
-        <v>78877</v>
+        <v>78885</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>130467073</v>
       </c>
       <c r="B21" t="n">
-        <v>91782</v>
+        <v>91795</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         <v>130467122</v>
       </c>
       <c r="B22" t="n">
-        <v>91818</v>
+        <v>91831</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>130466789</v>
       </c>
       <c r="B23" t="n">
-        <v>97835</v>
+        <v>97848</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 29387-2025 artfynd.xlsx
+++ b/artfynd/A 29387-2025 artfynd.xlsx
@@ -1933,7 +1933,7 @@
         <v>130466908</v>
       </c>
       <c r="B14" t="n">
-        <v>106037</v>
+        <v>106038</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>130466980</v>
       </c>
       <c r="B15" t="n">
-        <v>97216</v>
+        <v>97217</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>130466830</v>
       </c>
       <c r="B17" t="n">
-        <v>79838</v>
+        <v>79839</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>130467034</v>
       </c>
       <c r="B18" t="n">
-        <v>91795</v>
+        <v>91796</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>130466886</v>
       </c>
       <c r="B19" t="n">
-        <v>106037</v>
+        <v>106038</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         <v>130467204</v>
       </c>
       <c r="B20" t="n">
-        <v>78885</v>
+        <v>78886</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>130467073</v>
       </c>
       <c r="B21" t="n">
-        <v>91795</v>
+        <v>91796</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         <v>130467122</v>
       </c>
       <c r="B22" t="n">
-        <v>91831</v>
+        <v>91832</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>130466789</v>
       </c>
       <c r="B23" t="n">
-        <v>97848</v>
+        <v>97849</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 29387-2025 artfynd.xlsx
+++ b/artfynd/A 29387-2025 artfynd.xlsx
@@ -1933,7 +1933,7 @@
         <v>130466908</v>
       </c>
       <c r="B14" t="n">
-        <v>106038</v>
+        <v>106041</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>130466980</v>
       </c>
       <c r="B15" t="n">
-        <v>97217</v>
+        <v>97220</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>130466830</v>
       </c>
       <c r="B17" t="n">
-        <v>79839</v>
+        <v>79840</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>130467034</v>
       </c>
       <c r="B18" t="n">
-        <v>91796</v>
+        <v>91797</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v>130466886</v>
       </c>
       <c r="B19" t="n">
-        <v>106038</v>
+        <v>106041</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         <v>130467204</v>
       </c>
       <c r="B20" t="n">
-        <v>78886</v>
+        <v>78887</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>130467073</v>
       </c>
       <c r="B21" t="n">
-        <v>91796</v>
+        <v>91797</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         <v>130467122</v>
       </c>
       <c r="B22" t="n">
-        <v>91832</v>
+        <v>91833</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>130466789</v>
       </c>
       <c r="B23" t="n">
-        <v>97849</v>
+        <v>97852</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 29387-2025 artfynd.xlsx
+++ b/artfynd/A 29387-2025 artfynd.xlsx
@@ -2342,48 +2342,49 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130467034</v>
+        <v>130466886</v>
       </c>
       <c r="B18" t="n">
-        <v>91797</v>
+        <v>106041</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5442</v>
+        <v>221144</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hattberget, Ög</t>
+          <t>Ö Hattberget, Ög</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>560569</v>
+        <v>560839</v>
       </c>
       <c r="R18" t="n">
-        <v>6462203</v>
+        <v>6462220</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2443,49 +2444,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130466886</v>
+        <v>130467034</v>
       </c>
       <c r="B19" t="n">
-        <v>106041</v>
+        <v>91797</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221144</v>
+        <v>5442</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ö Hattberget, Ög</t>
+          <t>Hattberget, Ög</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>560839</v>
+        <v>560569</v>
       </c>
       <c r="R19" t="n">
-        <v>6462220</v>
+        <v>6462203</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 29387-2025 artfynd.xlsx
+++ b/artfynd/A 29387-2025 artfynd.xlsx
@@ -2342,49 +2342,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130466886</v>
+        <v>130467034</v>
       </c>
       <c r="B18" t="n">
-        <v>106041</v>
+        <v>91797</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221144</v>
+        <v>5442</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ö Hattberget, Ög</t>
+          <t>Hattberget, Ög</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>560839</v>
+        <v>560569</v>
       </c>
       <c r="R18" t="n">
-        <v>6462220</v>
+        <v>6462203</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2444,48 +2443,49 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130467034</v>
+        <v>130466886</v>
       </c>
       <c r="B19" t="n">
-        <v>91797</v>
+        <v>106041</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5442</v>
+        <v>221144</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hattberget, Ög</t>
+          <t>Ö Hattberget, Ög</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>560569</v>
+        <v>560839</v>
       </c>
       <c r="R19" t="n">
-        <v>6462203</v>
+        <v>6462220</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 29387-2025 artfynd.xlsx
+++ b/artfynd/A 29387-2025 artfynd.xlsx
@@ -1933,7 +1933,7 @@
         <v>130466908</v>
       </c>
       <c r="B14" t="n">
-        <v>106041</v>
+        <v>106055</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>130466980</v>
       </c>
       <c r="B15" t="n">
-        <v>97220</v>
+        <v>97229</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2342,48 +2342,49 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130467034</v>
+        <v>130466886</v>
       </c>
       <c r="B18" t="n">
-        <v>91797</v>
+        <v>106055</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5442</v>
+        <v>221144</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hattberget, Ög</t>
+          <t>Ö Hattberget, Ög</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>560569</v>
+        <v>560839</v>
       </c>
       <c r="R18" t="n">
-        <v>6462203</v>
+        <v>6462220</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2443,49 +2444,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130466886</v>
+        <v>130467034</v>
       </c>
       <c r="B19" t="n">
-        <v>106041</v>
+        <v>91805</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221144</v>
+        <v>5442</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ö Hattberget, Ög</t>
+          <t>Hattberget, Ög</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>560839</v>
+        <v>560569</v>
       </c>
       <c r="R19" t="n">
-        <v>6462220</v>
+        <v>6462203</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2649,7 +2649,7 @@
         <v>130467073</v>
       </c>
       <c r="B21" t="n">
-        <v>91797</v>
+        <v>91805</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         <v>130467122</v>
       </c>
       <c r="B22" t="n">
-        <v>91833</v>
+        <v>91841</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>130466789</v>
       </c>
       <c r="B23" t="n">
-        <v>97852</v>
+        <v>97861</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 29387-2025 artfynd.xlsx
+++ b/artfynd/A 29387-2025 artfynd.xlsx
@@ -1933,7 +1933,7 @@
         <v>130466908</v>
       </c>
       <c r="B14" t="n">
-        <v>106055</v>
+        <v>106093</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2342,49 +2342,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130466886</v>
+        <v>130467034</v>
       </c>
       <c r="B18" t="n">
-        <v>106055</v>
+        <v>91805</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221144</v>
+        <v>5442</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ö Hattberget, Ög</t>
+          <t>Hattberget, Ög</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>560839</v>
+        <v>560569</v>
       </c>
       <c r="R18" t="n">
-        <v>6462220</v>
+        <v>6462203</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2444,48 +2443,49 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130467034</v>
+        <v>130466886</v>
       </c>
       <c r="B19" t="n">
-        <v>91805</v>
+        <v>106093</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5442</v>
+        <v>221144</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hattberget, Ög</t>
+          <t>Ö Hattberget, Ög</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>560569</v>
+        <v>560839</v>
       </c>
       <c r="R19" t="n">
-        <v>6462203</v>
+        <v>6462220</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 29387-2025 artfynd.xlsx
+++ b/artfynd/A 29387-2025 artfynd.xlsx
@@ -3155,50 +3155,38 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134395971</v>
+        <v>134393436</v>
       </c>
       <c r="B26" t="n">
-        <v>58136</v>
+        <v>99181</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3206,10 +3194,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>560577</v>
+        <v>560630</v>
       </c>
       <c r="R26" t="n">
-        <v>6462026</v>
+        <v>6462205</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3244,12 +3232,18 @@
           <t>2026-06-12</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3268,38 +3262,50 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134393436</v>
+        <v>134395971</v>
       </c>
       <c r="B27" t="n">
-        <v>99181</v>
+        <v>58136</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3307,10 +3313,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>560630</v>
+        <v>560577</v>
       </c>
       <c r="R27" t="n">
-        <v>6462205</v>
+        <v>6462026</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3345,18 +3351,12 @@
           <t>2026-06-12</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3595,10 +3595,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134395849</v>
+        <v>134395624</v>
       </c>
       <c r="B30" t="n">
-        <v>79025</v>
+        <v>79978</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3606,21 +3606,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3633,10 +3633,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>560540</v>
+        <v>560566</v>
       </c>
       <c r="R30" t="n">
-        <v>6462083</v>
+        <v>6462140</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3696,10 +3696,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134395624</v>
+        <v>134395849</v>
       </c>
       <c r="B31" t="n">
-        <v>79978</v>
+        <v>79025</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3707,21 +3707,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3734,10 +3734,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>560566</v>
+        <v>560540</v>
       </c>
       <c r="R31" t="n">
-        <v>6462140</v>
+        <v>6462083</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3903,39 +3903,38 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>134395609</v>
+        <v>134395824</v>
       </c>
       <c r="B33" t="n">
-        <v>5181</v>
+        <v>99181</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -3943,10 +3942,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>560574</v>
+        <v>560547</v>
       </c>
       <c r="R33" t="n">
-        <v>6462089</v>
+        <v>6462156</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3979,6 +3978,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ett tiotal</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4006,38 +4010,39 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134395824</v>
+        <v>134395609</v>
       </c>
       <c r="B34" t="n">
-        <v>99181</v>
+        <v>5181</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4045,10 +4050,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>560547</v>
+        <v>560574</v>
       </c>
       <c r="R34" t="n">
-        <v>6462156</v>
+        <v>6462089</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4081,11 +4086,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ett tiotal</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4113,10 +4113,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>134395676</v>
+        <v>134393712</v>
       </c>
       <c r="B35" t="n">
-        <v>57972</v>
+        <v>79978</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4124,31 +4124,26 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4156,10 +4151,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>560566</v>
+        <v>560600</v>
       </c>
       <c r="R35" t="n">
-        <v>6462140</v>
+        <v>6462053</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4200,6 +4195,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4218,7 +4214,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>134395778</v>
+        <v>134395676</v>
       </c>
       <c r="B36" t="n">
         <v>57972</v>
@@ -4251,7 +4247,7 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -4261,10 +4257,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>560526</v>
+        <v>560566</v>
       </c>
       <c r="R36" t="n">
-        <v>6462132</v>
+        <v>6462140</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4297,11 +4293,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Boträd med äldre bo</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4328,10 +4319,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>134393712</v>
+        <v>134395778</v>
       </c>
       <c r="B37" t="n">
-        <v>79978</v>
+        <v>57972</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4339,26 +4330,31 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4366,10 +4362,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>560600</v>
+        <v>560526</v>
       </c>
       <c r="R37" t="n">
-        <v>6462053</v>
+        <v>6462132</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4404,13 +4400,17 @@
           <t>2026-06-12</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Boträd med äldre bo</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4429,42 +4429,38 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>134394466</v>
+        <v>134393697</v>
       </c>
       <c r="B38" t="n">
-        <v>58136</v>
+        <v>99181</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4472,10 +4468,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>560760</v>
+        <v>560606</v>
       </c>
       <c r="R38" t="n">
-        <v>6462230</v>
+        <v>6462093</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4502,17 +4498,17 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Den hördes och observerades. Även på berget mitt emot dagen innan hördes den så det är uppenbart att den har hemvist och häckningsrevir i den gamla kontinuitetsskogen på bägge bersgshöjder. Äldst är kontinuitetsskogen inom reviret på västra bergshöjden och likaledes avverkningsanmälan där med ca 150 till 160 år. Spridda tallar är ca 180 till 200 gamla och enstaka mellan ca. 220 och 300 år. På östra höjden och andra halvan av avverkningsanmälan är kontinuitetsskogen överlag ca 120 år gamla men bitvis även ca 100 år med spridda förekommande ca 160 till 200 åriga tallar och enstaka 200 till 230 åriga tallar.</t>
+          <t>Enstaka små bladrosetter som är svåra att upptäcka i markvegetationen.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4521,6 +4517,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4539,38 +4536,42 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>134393697</v>
+        <v>134394466</v>
       </c>
       <c r="B39" t="n">
-        <v>99181</v>
+        <v>58136</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4578,10 +4579,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>560606</v>
+        <v>560760</v>
       </c>
       <c r="R39" t="n">
-        <v>6462093</v>
+        <v>6462230</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4608,17 +4609,17 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Enstaka små bladrosetter som är svåra att upptäcka i markvegetationen.</t>
+          <t>Den hördes och observerades. Även på berget mitt emot dagen innan hördes den så det är uppenbart att den har hemvist och häckningsrevir i den gamla kontinuitetsskogen på bägge bersgshöjder. Äldst är kontinuitetsskogen inom reviret på västra bergshöjden och likaledes avverkningsanmälan där med ca 150 till 160 år. Spridda tallar är ca 180 till 200 gamla och enstaka mellan ca. 220 och 300 år. På östra höjden och andra halvan av avverkningsanmälan är kontinuitetsskogen överlag ca 120 år gamla men bitvis även ca 100 år med spridda förekommande ca 160 till 200 åriga tallar och enstaka 200 till 230 åriga tallar.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4627,7 +4628,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4753,39 +4753,37 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>134395789</v>
+        <v>134395958</v>
       </c>
       <c r="B41" t="n">
-        <v>5181</v>
+        <v>79025</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100526</v>
+        <v>353</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4793,10 +4791,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>560539</v>
+        <v>560542</v>
       </c>
       <c r="R41" t="n">
-        <v>6462137</v>
+        <v>6462045</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4856,37 +4854,39 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>134395958</v>
+        <v>134395789</v>
       </c>
       <c r="B42" t="n">
-        <v>79025</v>
+        <v>5181</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>353</v>
+        <v>100526</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -4894,10 +4894,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>560542</v>
+        <v>560539</v>
       </c>
       <c r="R42" t="n">
-        <v>6462045</v>
+        <v>6462137</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5058,10 +5058,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>134395831</v>
+        <v>134394493</v>
       </c>
       <c r="B44" t="n">
-        <v>91960</v>
+        <v>91981</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5069,24 +5069,28 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
@@ -5096,10 +5100,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>560547</v>
+        <v>560781</v>
       </c>
       <c r="R44" t="n">
-        <v>6462156</v>
+        <v>6462181</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5126,12 +5130,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5159,32 +5163,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>134394515</v>
+        <v>134395383</v>
       </c>
       <c r="B45" t="n">
-        <v>91960</v>
+        <v>93257</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5197,10 +5201,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>560817</v>
+        <v>560602</v>
       </c>
       <c r="R45" t="n">
-        <v>6462116</v>
+        <v>6462084</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5227,12 +5231,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5260,32 +5264,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>134395383</v>
+        <v>134395831</v>
       </c>
       <c r="B46" t="n">
-        <v>93257</v>
+        <v>91960</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5298,10 +5302,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>560602</v>
+        <v>560547</v>
       </c>
       <c r="R46" t="n">
-        <v>6462084</v>
+        <v>6462156</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5361,10 +5365,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>134394493</v>
+        <v>134394515</v>
       </c>
       <c r="B47" t="n">
-        <v>91981</v>
+        <v>91960</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5372,28 +5376,24 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
@@ -5403,10 +5403,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>560781</v>
+        <v>560817</v>
       </c>
       <c r="R47" t="n">
-        <v>6462181</v>
+        <v>6462116</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>

--- a/artfynd/A 29387-2025 artfynd.xlsx
+++ b/artfynd/A 29387-2025 artfynd.xlsx
@@ -3057,7 +3057,7 @@
         <v>134393447</v>
       </c>
       <c r="B25" t="n">
-        <v>91974</v>
+        <v>91981</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>134393436</v>
       </c>
       <c r="B26" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
         <v>134395624</v>
       </c>
       <c r="B30" t="n">
-        <v>79978</v>
+        <v>79985</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>134395849</v>
       </c>
       <c r="B31" t="n">
-        <v>79025</v>
+        <v>79032</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         <v>134395593</v>
       </c>
       <c r="B32" t="n">
-        <v>91960</v>
+        <v>91967</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3906,7 +3906,7 @@
         <v>134395824</v>
       </c>
       <c r="B33" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4113,10 +4113,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>134393712</v>
+        <v>134395778</v>
       </c>
       <c r="B35" t="n">
-        <v>79978</v>
+        <v>57972</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4124,26 +4124,31 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4151,10 +4156,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>560600</v>
+        <v>560526</v>
       </c>
       <c r="R35" t="n">
-        <v>6462053</v>
+        <v>6462132</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4189,13 +4194,17 @@
           <t>2026-06-12</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Boträd med äldre bo</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4214,10 +4223,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>134395676</v>
+        <v>134393712</v>
       </c>
       <c r="B36" t="n">
-        <v>57972</v>
+        <v>79985</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4225,31 +4234,26 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4257,10 +4261,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>560566</v>
+        <v>560600</v>
       </c>
       <c r="R36" t="n">
-        <v>6462140</v>
+        <v>6462053</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4301,6 +4305,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4319,7 +4324,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>134395778</v>
+        <v>134395676</v>
       </c>
       <c r="B37" t="n">
         <v>57972</v>
@@ -4352,7 +4357,7 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -4362,10 +4367,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>560526</v>
+        <v>560566</v>
       </c>
       <c r="R37" t="n">
-        <v>6462132</v>
+        <v>6462140</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4398,11 +4403,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Boträd med äldre bo</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4429,38 +4429,42 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>134393697</v>
+        <v>134394466</v>
       </c>
       <c r="B38" t="n">
-        <v>99181</v>
+        <v>58136</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4468,10 +4472,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>560606</v>
+        <v>560760</v>
       </c>
       <c r="R38" t="n">
-        <v>6462093</v>
+        <v>6462230</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4498,17 +4502,17 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Enstaka små bladrosetter som är svåra att upptäcka i markvegetationen.</t>
+          <t>Den hördes och observerades. Även på berget mitt emot dagen innan hördes den så det är uppenbart att den har hemvist och häckningsrevir i den gamla kontinuitetsskogen på bägge bersgshöjder. Äldst är kontinuitetsskogen inom reviret på västra bergshöjden och likaledes avverkningsanmälan där med ca 150 till 160 år. Spridda tallar är ca 180 till 200 gamla och enstaka mellan ca. 220 och 300 år. På östra höjden och andra halvan av avverkningsanmälan är kontinuitetsskogen överlag ca 120 år gamla men bitvis även ca 100 år med spridda förekommande ca 160 till 200 åriga tallar och enstaka 200 till 230 åriga tallar.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4517,7 +4521,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4536,42 +4539,38 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>134394466</v>
+        <v>134393697</v>
       </c>
       <c r="B39" t="n">
-        <v>58136</v>
+        <v>99188</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4579,10 +4578,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>560760</v>
+        <v>560606</v>
       </c>
       <c r="R39" t="n">
-        <v>6462230</v>
+        <v>6462093</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4609,17 +4608,17 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Den hördes och observerades. Även på berget mitt emot dagen innan hördes den så det är uppenbart att den har hemvist och häckningsrevir i den gamla kontinuitetsskogen på bägge bersgshöjder. Äldst är kontinuitetsskogen inom reviret på västra bergshöjden och likaledes avverkningsanmälan där med ca 150 till 160 år. Spridda tallar är ca 180 till 200 gamla och enstaka mellan ca. 220 och 300 år. På östra höjden och andra halvan av avverkningsanmälan är kontinuitetsskogen överlag ca 120 år gamla men bitvis även ca 100 år med spridda förekommande ca 160 till 200 åriga tallar och enstaka 200 till 230 åriga tallar.</t>
+          <t>Enstaka små bladrosetter som är svåra att upptäcka i markvegetationen.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4628,6 +4627,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4649,7 +4649,7 @@
         <v>134395500</v>
       </c>
       <c r="B40" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4756,7 +4756,7 @@
         <v>134395958</v>
       </c>
       <c r="B41" t="n">
-        <v>79025</v>
+        <v>79032</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4957,32 +4957,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>134395853</v>
+        <v>134395831</v>
       </c>
       <c r="B43" t="n">
-        <v>91923</v>
+        <v>91967</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4995,10 +4995,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>560540</v>
+        <v>560547</v>
       </c>
       <c r="R43" t="n">
-        <v>6462083</v>
+        <v>6462156</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5058,39 +5058,35 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>134394493</v>
+        <v>134395383</v>
       </c>
       <c r="B44" t="n">
-        <v>91981</v>
+        <v>93264</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
@@ -5100,10 +5096,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>560781</v>
+        <v>560602</v>
       </c>
       <c r="R44" t="n">
-        <v>6462181</v>
+        <v>6462084</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5130,12 +5126,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5163,35 +5159,39 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>134395383</v>
+        <v>134394493</v>
       </c>
       <c r="B45" t="n">
-        <v>93257</v>
+        <v>91988</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
@@ -5201,10 +5201,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>560602</v>
+        <v>560781</v>
       </c>
       <c r="R45" t="n">
-        <v>6462084</v>
+        <v>6462181</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5231,12 +5231,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5264,32 +5264,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>134395831</v>
+        <v>134395853</v>
       </c>
       <c r="B46" t="n">
-        <v>91960</v>
+        <v>91930</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5302,10 +5302,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>560547</v>
+        <v>560540</v>
       </c>
       <c r="R46" t="n">
-        <v>6462156</v>
+        <v>6462083</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5368,7 +5368,7 @@
         <v>134394515</v>
       </c>
       <c r="B47" t="n">
-        <v>91960</v>
+        <v>91967</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 29387-2025 artfynd.xlsx
+++ b/artfynd/A 29387-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY47"/>
+  <dimension ref="A1:AY66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126826562</v>
+        <v>130466980</v>
       </c>
       <c r="B2" t="n">
-        <v>79636</v>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,40 +686,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hattberget/Risten, Ög</t>
+          <t>Hattberget, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>560782</v>
+        <v>560633</v>
       </c>
       <c r="R2" t="n">
-        <v>6462146</v>
+        <v>6462268</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,12 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,64 +765,63 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Madeleine Askelöf</t>
+          <t>Magnus Wadstein</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Madeleine Askelöf</t>
+          <t>Magnus Wadstein</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126826277</v>
+        <v>126848866</v>
       </c>
       <c r="B3" t="n">
-        <v>105486</v>
+        <v>92205</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>73</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Fomitopsis pulvinascens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Pilát) Niemelä &amp; Miettinen</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hattberget/Risten, Ög</t>
+          <t>Lakviken/Risten, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>560835</v>
+        <v>560639</v>
       </c>
       <c r="R3" t="n">
-        <v>6462218</v>
+        <v>6462152</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -851,11 +851,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-07-14</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Flera</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,10 +878,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126760235</v>
+        <v>130467204</v>
       </c>
       <c r="B4" t="n">
-        <v>79636</v>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -894,21 +889,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -917,14 +912,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hattberget/Risten, Ög</t>
+          <t>Hattberget, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560794</v>
+        <v>560538</v>
       </c>
       <c r="R4" t="n">
-        <v>6462189</v>
+        <v>6462052</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -951,12 +946,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -972,64 +967,63 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Madeleine Askelöf</t>
+          <t>Magnus Wadstein</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Madeleine Askelöf</t>
+          <t>Magnus Wadstein</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126826308</v>
+        <v>130467241</v>
       </c>
       <c r="B5" t="n">
-        <v>105486</v>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hattberget/Risten, Ög</t>
+          <t>Hattberget, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>560799</v>
+        <v>560490</v>
       </c>
       <c r="R5" t="n">
-        <v>6462286</v>
+        <v>6462137</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1053,17 +1047,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Flera</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1079,22 +1068,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Madeleine Askelöf</t>
+          <t>Magnus Wadstein</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Madeleine Askelöf</t>
+          <t>Magnus Wadstein</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126848655</v>
+        <v>134395849</v>
       </c>
       <c r="B6" t="n">
-        <v>91350</v>
+        <v>79039</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1102,21 +1091,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1125,17 +1114,17 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lakviken/Risten, Ög</t>
+          <t>Risten-Myssmyra , Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>560634</v>
+        <v>560540</v>
       </c>
       <c r="R6" t="n">
-        <v>6462096</v>
+        <v>6462083</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1159,12 +1148,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1180,44 +1169,44 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Madeleine Askelöf</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Madeleine Askelöf</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126848714</v>
+        <v>134395958</v>
       </c>
       <c r="B7" t="n">
-        <v>91295</v>
+        <v>79039</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1226,17 +1215,17 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lakviken/Risten, Ög</t>
+          <t>Risten-Myssmyra , Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>560616</v>
+        <v>560542</v>
       </c>
       <c r="R7" t="n">
-        <v>6462133</v>
+        <v>6462045</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1260,12 +1249,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1281,44 +1270,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Madeleine Askelöf</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Madeleine Askelöf</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126848794</v>
+        <v>134393790</v>
       </c>
       <c r="B8" t="n">
-        <v>91951</v>
+        <v>91972</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5454</v>
+        <v>1110</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Tallharticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Pelloporus triqueter</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,17 +1316,17 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lakviken/Risten, Ög</t>
+          <t>Risten-Myssmyra , Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>560633</v>
+        <v>560600</v>
       </c>
       <c r="R8" t="n">
-        <v>6462133</v>
+        <v>6462020</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1361,12 +1350,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På stammbasen av en ca. 200 årig tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1382,22 +1376,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Madeleine Askelöf</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Madeleine Askelöf</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126848641</v>
+        <v>134393416</v>
       </c>
       <c r="B9" t="n">
-        <v>79636</v>
+        <v>91974</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1405,21 +1399,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1428,17 +1422,17 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lakviken/Risten, Ög</t>
+          <t>Risten-Myssmyra , Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>560608</v>
+        <v>560644</v>
       </c>
       <c r="R9" t="n">
-        <v>6462081</v>
+        <v>6462195</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1462,12 +1456,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1483,22 +1477,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Madeleine Askelöf</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Madeleine Askelöf</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126848471</v>
+        <v>134394086</v>
       </c>
       <c r="B10" t="n">
-        <v>5493</v>
+        <v>91974</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1506,42 +1500,40 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>101410</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lakviken/Risten, Ög</t>
+          <t>Risten-Myssmyra , Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>560569</v>
+        <v>560658</v>
       </c>
       <c r="R10" t="n">
-        <v>6462191</v>
+        <v>6462155</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1565,12 +1557,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1586,64 +1578,63 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Madeleine Askelöf</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Madeleine Askelöf</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127748895</v>
+        <v>134394515</v>
       </c>
       <c r="B11" t="n">
-        <v>96173</v>
+        <v>91974</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2180</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hattberget/Risten, Ög</t>
+          <t>Risten-Myssmyra , Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>560796</v>
+        <v>560817</v>
       </c>
       <c r="R11" t="n">
-        <v>6462042</v>
+        <v>6462116</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1667,17 +1658,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Flera</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1693,22 +1679,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Charlotte Erbs</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Charlotte Erbs</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127748920</v>
+        <v>134395593</v>
       </c>
       <c r="B12" t="n">
-        <v>57845</v>
+        <v>91974</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1716,53 +1702,40 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hattberget/Risten, Ög</t>
+          <t>Risten-Myssmyra , Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>560789</v>
+        <v>560574</v>
       </c>
       <c r="R12" t="n">
-        <v>6462042</v>
+        <v>6462089</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1786,17 +1759,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Hört från två håll</t>
+          <t>En gammal fruktkropp</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1805,72 +1778,67 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Charlotte Erbs</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Charlotte Erbs</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130466959</v>
+        <v>134395831</v>
       </c>
       <c r="B13" t="n">
-        <v>5177</v>
+        <v>91974</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hattberget, Ög</t>
+          <t>Risten-Myssmyra , Ög</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>560584</v>
+        <v>560547</v>
       </c>
       <c r="R13" t="n">
-        <v>6462350</v>
+        <v>6462156</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1897,12 +1865,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1918,61 +1886,60 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Magnus Wadstein</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Magnus Wadstein</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130466908</v>
+        <v>134393447</v>
       </c>
       <c r="B14" t="n">
-        <v>106107</v>
+        <v>91988</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221144</v>
+        <v>1204</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ö Hattberget, Ög</t>
+          <t>Risten-Myssmyra , Ög</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>560805</v>
+        <v>560626</v>
       </c>
       <c r="R14" t="n">
-        <v>6462293</v>
+        <v>6462193</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1999,12 +1966,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2020,44 +1987,44 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Magnus Wadstein</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Magnus Wadstein</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130466980</v>
+        <v>127748895</v>
       </c>
       <c r="B15" t="n">
-        <v>97243</v>
+        <v>96708</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>53</v>
+        <v>2180</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2067,17 +2034,17 @@
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hattberget, Ög</t>
+          <t>Hattberget/Risten, Ög</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>560633</v>
+        <v>560796</v>
       </c>
       <c r="R15" t="n">
-        <v>6462268</v>
+        <v>6462042</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2101,12 +2068,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Flera</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2122,66 +2094,61 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Magnus Wadstein</t>
+          <t>Charlotte Erbs</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Magnus Wadstein</t>
+          <t>Charlotte Erbs</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130467040</v>
+        <v>134393403</v>
       </c>
       <c r="B16" t="n">
-        <v>5493</v>
+        <v>96783</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>101410</v>
+        <v>2180</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hattberget, Ög</t>
+          <t>Risten-Myssmyra , Ög</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>560569</v>
+        <v>560660</v>
       </c>
       <c r="R16" t="n">
-        <v>6462203</v>
+        <v>6462201</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2208,12 +2175,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2229,44 +2196,44 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Magnus Wadstein</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Magnus Wadstein</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130466830</v>
+        <v>134395412</v>
       </c>
       <c r="B17" t="n">
-        <v>79854</v>
+        <v>92188</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>3008</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Timmerticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Amyloporia sinuosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Rajchenb. &amp; al.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2275,14 +2242,14 @@
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Ö Hattberget, Ög</t>
+          <t>Risten-Myssmyra , Ög</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>560785</v>
+        <v>560571</v>
       </c>
       <c r="R17" t="n">
-        <v>6462144</v>
+        <v>6462061</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2309,12 +2276,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2330,22 +2297,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Magnus Wadstein</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Magnus Wadstein</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130466886</v>
+        <v>134395792</v>
       </c>
       <c r="B18" t="n">
-        <v>106107</v>
+        <v>92188</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2353,38 +2320,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221144</v>
+        <v>3008</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Timmerticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Amyloporia sinuosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.) Rajchenb. &amp; al.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ö Hattberget, Ög</t>
+          <t>Risten-Myssmyra , Ög</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>560839</v>
+        <v>560539</v>
       </c>
       <c r="R18" t="n">
-        <v>6462220</v>
+        <v>6462137</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2411,12 +2377,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2432,22 +2398,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Magnus Wadstein</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Magnus Wadstein</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130467034</v>
+        <v>134395383</v>
       </c>
       <c r="B19" t="n">
-        <v>91819</v>
+        <v>93271</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2455,21 +2421,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2478,14 +2444,14 @@
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hattberget, Ög</t>
+          <t>Risten-Myssmyra , Ög</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>560569</v>
+        <v>560602</v>
       </c>
       <c r="R19" t="n">
-        <v>6462203</v>
+        <v>6462084</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2512,12 +2478,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2533,44 +2499,44 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Magnus Wadstein</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Magnus Wadstein</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130467204</v>
+        <v>130467122</v>
       </c>
       <c r="B20" t="n">
-        <v>78901</v>
+        <v>91966</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>5321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2583,10 +2549,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>560538</v>
+        <v>560632</v>
       </c>
       <c r="R20" t="n">
-        <v>6462052</v>
+        <v>6462158</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2646,10 +2612,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130467073</v>
+        <v>126848655</v>
       </c>
       <c r="B21" t="n">
-        <v>91819</v>
+        <v>91930</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2680,17 +2646,17 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Hattberget, Ög</t>
+          <t>Lakviken/Risten, Ög</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>560607</v>
+        <v>560634</v>
       </c>
       <c r="R21" t="n">
-        <v>6462162</v>
+        <v>6462096</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2714,12 +2680,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2735,44 +2701,44 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Magnus Wadstein</t>
+          <t>Madeleine Askelöf</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Magnus Wadstein</t>
+          <t>Madeleine Askelöf</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130467122</v>
+        <v>130467034</v>
       </c>
       <c r="B22" t="n">
-        <v>91855</v>
+        <v>91930</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5321</v>
+        <v>5442</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2785,10 +2751,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>560632</v>
+        <v>560569</v>
       </c>
       <c r="R22" t="n">
-        <v>6462158</v>
+        <v>6462203</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2848,34 +2814,37 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130466789</v>
+        <v>130467073</v>
       </c>
       <c r="B23" t="n">
-        <v>97875</v>
+        <v>91930</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>224358</v>
+        <v>5442</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vanlig plattlummer</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum subsp. complanatum</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2883,10 +2852,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>560779</v>
+        <v>560607</v>
       </c>
       <c r="R23" t="n">
-        <v>6462163</v>
+        <v>6462162</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2919,11 +2888,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-01</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>ca 5 x 10 m2</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2951,50 +2915,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134394521</v>
+        <v>130467163</v>
       </c>
       <c r="B24" t="n">
-        <v>5181</v>
+        <v>91930</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100526</v>
+        <v>5442</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Risten-Myssmyra , Ög</t>
+          <t>Hattberget, Ög</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>560817</v>
+        <v>560637</v>
       </c>
       <c r="R24" t="n">
-        <v>6462116</v>
+        <v>6462095</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,12 +2983,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3042,22 +3004,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Magnus Wadstein</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Magnus Wadstein</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134393447</v>
+        <v>134394493</v>
       </c>
       <c r="B25" t="n">
-        <v>91981</v>
+        <v>91995</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3065,24 +3027,28 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1204</v>
+        <v>5442</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
@@ -3092,10 +3058,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>560626</v>
+        <v>560781</v>
       </c>
       <c r="R25" t="n">
-        <v>6462193</v>
+        <v>6462181</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3122,12 +3088,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3155,52 +3121,51 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134393436</v>
+        <v>126848714</v>
       </c>
       <c r="B26" t="n">
-        <v>99188</v>
+        <v>91872</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Risten-Myssmyra , Ög</t>
+          <t>Lakviken/Risten, Ög</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>560630</v>
+        <v>560616</v>
       </c>
       <c r="R26" t="n">
-        <v>6462205</v>
+        <v>6462133</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3224,17 +3189,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3250,62 +3210,49 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Madeleine Askelöf</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Madeleine Askelöf</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134395971</v>
+        <v>134395853</v>
       </c>
       <c r="B27" t="n">
-        <v>58136</v>
+        <v>91937</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3313,10 +3260,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>560577</v>
+        <v>560540</v>
       </c>
       <c r="R27" t="n">
-        <v>6462026</v>
+        <v>6462083</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3357,6 +3304,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3375,10 +3323,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134393493</v>
+        <v>126848794</v>
       </c>
       <c r="B28" t="n">
-        <v>57972</v>
+        <v>92556</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3386,57 +3334,40 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>5454</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Risten-Myssmyra , Ög</t>
+          <t>Lakviken/Risten, Ög</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>560595</v>
+        <v>560633</v>
       </c>
       <c r="R28" t="n">
-        <v>6462119</v>
+        <v>6462133</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3460,12 +3391,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3474,68 +3405,67 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Madeleine Askelöf</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Madeleine Askelöf</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134395409</v>
+        <v>126760235</v>
       </c>
       <c r="B29" t="n">
-        <v>8460</v>
+        <v>79946</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Risten-Myssmyra , Ög</t>
+          <t>Hattberget/Risten, Ög</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>560571</v>
+        <v>560794</v>
       </c>
       <c r="R29" t="n">
-        <v>6462061</v>
+        <v>6462189</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3562,12 +3492,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3583,22 +3513,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Madeleine Askelöf</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Madeleine Askelöf</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134395624</v>
+        <v>126826562</v>
       </c>
       <c r="B30" t="n">
-        <v>79985</v>
+        <v>79946</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3629,17 +3559,17 @@
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Risten-Myssmyra , Ög</t>
+          <t>Hattberget/Risten, Ög</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>560566</v>
+        <v>560782</v>
       </c>
       <c r="R30" t="n">
-        <v>6462140</v>
+        <v>6462146</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3663,12 +3593,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3684,22 +3614,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Madeleine Askelöf</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Madeleine Askelöf</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134395849</v>
+        <v>126848641</v>
       </c>
       <c r="B31" t="n">
-        <v>79032</v>
+        <v>79946</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3707,21 +3637,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3730,17 +3660,17 @@
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Risten-Myssmyra , Ög</t>
+          <t>Lakviken/Risten, Ög</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>560540</v>
+        <v>560608</v>
       </c>
       <c r="R31" t="n">
-        <v>6462083</v>
+        <v>6462081</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3764,12 +3694,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3785,22 +3715,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Madeleine Askelöf</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Madeleine Askelöf</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>134395593</v>
+        <v>126848683</v>
       </c>
       <c r="B32" t="n">
-        <v>91967</v>
+        <v>79946</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3808,21 +3738,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3831,17 +3761,17 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Risten-Myssmyra , Ög</t>
+          <t>Lakviken/Risten, Ög</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>560574</v>
+        <v>560638</v>
       </c>
       <c r="R32" t="n">
-        <v>6462089</v>
+        <v>6462100</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3865,17 +3795,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>En gammal fruktkropp</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3891,61 +3816,60 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Madeleine Askelöf</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Madeleine Askelöf</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>134395824</v>
+        <v>130466830</v>
       </c>
       <c r="B33" t="n">
-        <v>99188</v>
+        <v>79946</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Risten-Myssmyra , Ög</t>
+          <t>Ö Hattberget, Ög</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>560547</v>
+        <v>560785</v>
       </c>
       <c r="R33" t="n">
-        <v>6462156</v>
+        <v>6462144</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3972,17 +3896,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ett tiotal</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3998,62 +3917,60 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Magnus Wadstein</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Magnus Wadstein</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134395609</v>
+        <v>130467166</v>
       </c>
       <c r="B34" t="n">
-        <v>5181</v>
+        <v>79946</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100526</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Risten-Myssmyra , Ög</t>
+          <t>Hattberget, Ög</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>560574</v>
+        <v>560637</v>
       </c>
       <c r="R34" t="n">
-        <v>6462089</v>
+        <v>6462095</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4080,12 +3997,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4101,22 +4018,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Magnus Wadstein</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Magnus Wadstein</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>134395778</v>
+        <v>134393712</v>
       </c>
       <c r="B35" t="n">
-        <v>57972</v>
+        <v>79992</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4124,31 +4041,26 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4156,10 +4068,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>560526</v>
+        <v>560600</v>
       </c>
       <c r="R35" t="n">
-        <v>6462132</v>
+        <v>6462053</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4194,17 +4106,13 @@
           <t>2026-06-12</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Boträd med äldre bo</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4223,10 +4131,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>134393712</v>
+        <v>134393727</v>
       </c>
       <c r="B36" t="n">
-        <v>79985</v>
+        <v>79992</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4261,10 +4169,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>560600</v>
+        <v>560615</v>
       </c>
       <c r="R36" t="n">
-        <v>6462053</v>
+        <v>6462019</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4324,10 +4232,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>134395676</v>
+        <v>134395374</v>
       </c>
       <c r="B37" t="n">
-        <v>57972</v>
+        <v>79992</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4335,31 +4243,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4367,10 +4270,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>560566</v>
+        <v>560655</v>
       </c>
       <c r="R37" t="n">
-        <v>6462140</v>
+        <v>6462080</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4411,6 +4314,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4429,10 +4333,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>134394466</v>
+        <v>134395624</v>
       </c>
       <c r="B38" t="n">
-        <v>58136</v>
+        <v>79992</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4440,31 +4344,26 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4472,10 +4371,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>560760</v>
+        <v>560566</v>
       </c>
       <c r="R38" t="n">
-        <v>6462230</v>
+        <v>6462140</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4502,17 +4401,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Den hördes och observerades. Även på berget mitt emot dagen innan hördes den så det är uppenbart att den har hemvist och häckningsrevir i den gamla kontinuitetsskogen på bägge bersgshöjder. Äldst är kontinuitetsskogen inom reviret på västra bergshöjden och likaledes avverkningsanmälan där med ca 150 till 160 år. Spridda tallar är ca 180 till 200 gamla och enstaka mellan ca. 220 och 300 år. På östra höjden och andra halvan av avverkningsanmälan är kontinuitetsskogen överlag ca 120 år gamla men bitvis även ca 100 år med spridda förekommande ca 160 till 200 åriga tallar och enstaka 200 till 230 åriga tallar.</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4521,6 +4415,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4539,38 +4434,37 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>134393697</v>
+        <v>134395981</v>
       </c>
       <c r="B39" t="n">
-        <v>99188</v>
+        <v>79992</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4578,10 +4472,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>560606</v>
+        <v>560589</v>
       </c>
       <c r="R39" t="n">
-        <v>6462093</v>
+        <v>6462005</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4614,11 +4508,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Enstaka små bladrosetter som är svåra att upptäcka i markvegetationen.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4646,52 +4535,68 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>134395500</v>
+        <v>126848899</v>
       </c>
       <c r="B40" t="n">
-        <v>99188</v>
+        <v>57966</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>100048</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Risten-Myssmyra , Ög</t>
+          <t>Lakviken/Risten, Ög</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>560572</v>
+        <v>560642</v>
       </c>
       <c r="R40" t="n">
-        <v>6462103</v>
+        <v>6462150</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4715,17 +4620,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Enstaka små rosetter</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4734,70 +4634,86 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Madeleine Askelöf</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Madeleine Askelöf</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>134395958</v>
+        <v>126848842</v>
       </c>
       <c r="B41" t="n">
-        <v>79032</v>
+        <v>57950</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>353</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Risten-Myssmyra , Ög</t>
+          <t>Lakviken/Risten, Ög</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>560542</v>
+        <v>560663</v>
       </c>
       <c r="R41" t="n">
-        <v>6462045</v>
+        <v>6462145</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4821,12 +4737,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4835,29 +4751,28 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Madeleine Askelöf</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Madeleine Askelöf</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>134395789</v>
+        <v>134393493</v>
       </c>
       <c r="B42" t="n">
-        <v>5181</v>
+        <v>57972</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4865,28 +4780,43 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -4894,10 +4824,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>560539</v>
+        <v>560595</v>
       </c>
       <c r="R42" t="n">
-        <v>6462137</v>
+        <v>6462119</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4938,7 +4868,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4957,37 +4886,54 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>134395831</v>
+        <v>134394804</v>
       </c>
       <c r="B43" t="n">
-        <v>91967</v>
+        <v>57972</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -4995,10 +4941,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>560547</v>
+        <v>560812</v>
       </c>
       <c r="R43" t="n">
-        <v>6462156</v>
+        <v>6462032</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5025,12 +4971,17 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Spillkråkorna observerades och hördes livlig under de två fältbesök 12 och 13 juni 2026. Förutom revir kan det antas att de häckar i den kvarvarande gamla kontinuitetsskogen på höjderna.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5039,7 +4990,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5058,10 +5008,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>134395383</v>
+        <v>134395676</v>
       </c>
       <c r="B44" t="n">
-        <v>93264</v>
+        <v>57972</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5069,26 +5019,31 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5096,10 +5051,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>560602</v>
+        <v>560566</v>
       </c>
       <c r="R44" t="n">
-        <v>6462084</v>
+        <v>6462140</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5140,7 +5095,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5159,41 +5113,42 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>134394493</v>
+        <v>134395778</v>
       </c>
       <c r="B45" t="n">
-        <v>91988</v>
+        <v>57972</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5201,10 +5156,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>560781</v>
+        <v>560526</v>
       </c>
       <c r="R45" t="n">
-        <v>6462181</v>
+        <v>6462132</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5231,12 +5186,17 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Boträd med äldre bo</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5245,7 +5205,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5264,10 +5223,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>134395853</v>
+        <v>134396010</v>
       </c>
       <c r="B46" t="n">
-        <v>91930</v>
+        <v>57162</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5275,26 +5234,27 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5302,10 +5262,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>560540</v>
+        <v>560589</v>
       </c>
       <c r="R46" t="n">
-        <v>6462083</v>
+        <v>6462005</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5340,13 +5300,17 @@
           <t>2026-06-12</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Lega respektive sandbad framför rotvälta</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5365,48 +5329,54 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>134394515</v>
+        <v>130466959</v>
       </c>
       <c r="B47" t="n">
-        <v>91967</v>
+        <v>5179</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Risten-Myssmyra , Ög</t>
+          <t>Hattberget, Ög</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>560817</v>
+        <v>560584</v>
       </c>
       <c r="R47" t="n">
-        <v>6462116</v>
+        <v>6462350</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5433,12 +5403,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5454,15 +5424,2032 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
+          <t>Magnus Wadstein</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Magnus Wadstein</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>134394521</v>
+      </c>
+      <c r="B48" t="n">
+        <v>5181</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Risten-Myssmyra , Ög</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>560817</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6462116</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
           <t>Steve Daurer</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
+      <c r="AX48" t="inlineStr">
         <is>
           <t>Steve Daurer</t>
         </is>
       </c>
-      <c r="AY47" t="inlineStr"/>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>134395609</v>
+      </c>
+      <c r="B49" t="n">
+        <v>5181</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Risten-Myssmyra , Ög</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>560574</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6462089</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>134395789</v>
+      </c>
+      <c r="B50" t="n">
+        <v>5181</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Risten-Myssmyra , Ög</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>560539</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6462137</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>126848471</v>
+      </c>
+      <c r="B51" t="n">
+        <v>5495</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>101410</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Reliktbock</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Nothorhina muricata</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Lakviken/Risten, Ög</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>560569</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6462191</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Madeleine Askelöf</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Madeleine Askelöf</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>130467040</v>
+      </c>
+      <c r="B52" t="n">
+        <v>5495</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>101410</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Reliktbock</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Nothorhina muricata</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Hattberget, Ög</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>560569</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6462203</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Magnus Wadstein</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Magnus Wadstein</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>127748920</v>
+      </c>
+      <c r="B53" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Hattberget/Risten, Ög</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>560789</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6462042</v>
+      </c>
+      <c r="S53" t="n">
+        <v>5</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Hört från två håll</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Charlotte Erbs</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Charlotte Erbs</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>134394466</v>
+      </c>
+      <c r="B54" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Risten-Myssmyra , Ög</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>560760</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6462230</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Den hördes och observerades. Även på berget mitt emot dagen innan hördes den så det är uppenbart att den har hemvist och häckningsrevir i den gamla kontinuitetsskogen på bägge bersgshöjder. Äldst är kontinuitetsskogen inom reviret på västra bergshöjden och likaledes avverkningsanmälan där med ca 150 till 160 år. Spridda tallar är ca 180 till 200 gamla och enstaka mellan ca. 220 och 300 år. På östra höjden och andra halvan av avverkningsanmälan är kontinuitetsskogen överlag ca 120 år gamla men bitvis även ca 100 år med spridda förekommande ca 160 till 200 åriga tallar och enstaka 200 till 230 åriga tallar.</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>134395971</v>
+      </c>
+      <c r="B55" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Risten-Myssmyra , Ög</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>560577</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6462026</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>134395945</v>
+      </c>
+      <c r="B56" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Risten-Myssmyra , Ög</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>560540</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6462083</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>134395409</v>
+      </c>
+      <c r="B57" t="n">
+        <v>8460</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Risten-Myssmyra , Ög</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>560571</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6462061</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>134393436</v>
+      </c>
+      <c r="B58" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Risten-Myssmyra , Ög</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>560630</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6462205</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>134393697</v>
+      </c>
+      <c r="B59" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Risten-Myssmyra , Ög</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>560606</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6462093</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Enstaka små bladrosetter som är svåra att upptäcka i markvegetationen.</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>134395500</v>
+      </c>
+      <c r="B60" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Risten-Myssmyra , Ög</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>560572</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6462103</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Enstaka små rosetter</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>134395824</v>
+      </c>
+      <c r="B61" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Risten-Myssmyra , Ög</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>560547</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6462156</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ett tiotal</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>126826277</v>
+      </c>
+      <c r="B62" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Hattberget/Risten, Ög</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>560835</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6462218</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Flera</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Madeleine Askelöf</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Madeleine Askelöf</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>126826308</v>
+      </c>
+      <c r="B63" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Hattberget/Risten, Ög</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>560799</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6462286</v>
+      </c>
+      <c r="S63" t="n">
+        <v>5</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Flera</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Madeleine Askelöf</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Madeleine Askelöf</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>130466886</v>
+      </c>
+      <c r="B64" t="n">
+        <v>106243</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Ö Hattberget, Ög</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>560839</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6462220</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Magnus Wadstein</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Magnus Wadstein</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>130466908</v>
+      </c>
+      <c r="B65" t="n">
+        <v>106243</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Ö Hattberget, Ög</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>560805</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6462293</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Magnus Wadstein</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Magnus Wadstein</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>130466789</v>
+      </c>
+      <c r="B66" t="n">
+        <v>97990</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>224358</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Vanlig plattlummer</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum subsp. complanatum</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Hattberget, Ög</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>560779</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6462163</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>ca 5 x 10 m2</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Magnus Wadstein</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Magnus Wadstein</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
